--- a/outputs/reports/easy_ensemble_v2/feature_importance_top10.xlsx
+++ b/outputs/reports/easy_ensemble_v2/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2342891032138918</v>
+        <v>0.2862142282496265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04995247063043684</v>
+        <v>0.07278511534381027</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=28.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2169346663918652</v>
+        <v>0.2770658544994826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04625235404896427</v>
+        <v>0.07045865714260663</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.69%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=27.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1177880874367498</v>
+        <v>0.07052062981266526</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02511344274056149</v>
+        <v>0.01793360241530789</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=7.05%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.08249876971091312</v>
+        <v>0.06964142052637631</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01758945386064037</v>
+        <v>0.01771001692235302</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=8.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.96%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.07900769298714182</v>
+        <v>0.06402712331915868</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01684512599766852</v>
+        <v>0.01628228472224252</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.06972058767860208</v>
+        <v>0.04801746925640723</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01486503452605159</v>
+        <v>0.01221098287013628</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=4.80%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>누적자부담집행금액</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05652179399282405</v>
+        <v>0.03201930812550288</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01205093713568295</v>
+        <v>0.008142603704212492</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 누적자부담집행금액(CUMU_PYHWY_EXE_AMT). 기여도(정규화 비중)=3.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0448960878910108</v>
+        <v>0.02490518331226298</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009572235673930618</v>
+        <v>0.006333460957296644</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=2.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03046069594404178</v>
+        <v>0.02120445925755662</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0064944847995696</v>
+        <v>0.005392356006558519</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.05%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02416834560818392</v>
+        <v>0.01723939777037119</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005152901085104633</v>
+        <v>0.004384029273624801</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.42%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=1.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
